--- a/EXCEL/Exercise Files/Chapter04/Chapter_4_Challenge.xlsx
+++ b/EXCEL/Exercise Files/Chapter04/Chapter_4_Challenge.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Writing\Lynda\Data Analysis Fundamentals 20220331 Refresh\Exercise Files\Chapter04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B293FD-E0DC-4815-85FF-FB3D2BB7FF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11BF547A-989B-4105-8CCF-04361964690C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25875" yWindow="15" windowWidth="25695" windowHeight="21555" xr2:uid="{EB1F3AA5-A9F3-4433-9415-965F6145CBE0}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" activeTab="1" xr2:uid="{EB1F3AA5-A9F3-4433-9415-965F6145CBE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -586,21 +585,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BCA16AF-5C26-472D-A865-838B4E64A56E}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" customWidth="1"/>
-    <col min="4" max="4" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" customWidth="1"/>
+    <col min="4" max="4" width="36.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -610,9 +609,12 @@
       <c r="D3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="15">
+        <f>_xlfn.NORM.DIST(119,B3,B4,TRUE)</f>
+        <v>0.22878408753125365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -622,28 +624,43 @@
       <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="15"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="15">
+        <f>1-_xlfn.NORM.DIST(185,B3,B4,TRUE)</f>
+        <v>0.12654895447355785</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E6" s="17"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" s="15">
+        <f>-(_xlfn.NORM.DIST(119,B3,B4,TRUE)-_xlfn.NORM.DIST(185,B3,B4,TRUE))</f>
+        <v>0.64466695799518847</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E6" s="17">
+        <f>SUM(E3:E5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="16">
+        <f>_xlfn.NORM.INV(42%,B3,B4)</f>
+        <v>137.93372823003523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="16">
+        <f>_xlfn.NORM.INV(1-18%,B3,B4)</f>
+        <v>177.03777807449848</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -653,29 +670,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D28F71-AE87-458D-A1C6-99DFE508DFA5}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -685,7 +702,7 @@
       </c>
       <c r="E3" s="7"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -699,13 +716,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="9"/>
       <c r="D5" s="8"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>6</v>
       </c>
@@ -740,15 +757,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>1</v>
       </c>
-      <c r="B7" s="18"/>
+      <c r="B7" s="18">
+        <f>_xlfn.POISSON.DIST(A7,$B$4,TRUE)</f>
+        <v>3.0191636511226068E-3</v>
+      </c>
       <c r="D7" s="8">
         <v>1</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="18">
+        <f>_xlfn.EXPON.DIST(D7,1/$E$4,TRUE)</f>
+        <v>0.22119921692859512</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -771,488 +794,566 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>2</v>
       </c>
-      <c r="B8" s="18"/>
+      <c r="B8" s="18">
+        <f t="shared" ref="B8:B20" si="0">_xlfn.POISSON.DIST(A8,$B$4,TRUE)</f>
+        <v>1.3753967744002987E-2</v>
+      </c>
       <c r="D8" s="8">
         <v>2</v>
       </c>
-      <c r="E8" s="18"/>
+      <c r="E8" s="18">
+        <f t="shared" ref="E8:E20" si="1">_xlfn.EXPON.DIST(D8,1/$E$4,TRUE)</f>
+        <v>0.39346934028736658</v>
+      </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8">
         <f ca="1">_xlfn.XLOOKUP(RAND(),$B$7:$B$21,$A$7:$A$21,$B$4,1,1)</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <f ca="1">I7+H8</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <f ca="1">MAX(I8,L7+1)</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <f ca="1">_xlfn.XLOOKUP(RAND(),$E$7:$E$21,$D$7:$D$21,$E$4,1,1)</f>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <f ca="1">J8+K8</f>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <f ca="1">J8-I8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>3</v>
       </c>
-      <c r="B9" s="18"/>
+      <c r="B9" s="18">
+        <f t="shared" si="0"/>
+        <v>4.2380111991683997E-2</v>
+      </c>
       <c r="D9" s="8">
         <v>3</v>
       </c>
-      <c r="E9" s="18"/>
+      <c r="E9" s="18">
+        <f t="shared" si="1"/>
+        <v>0.52763344725898531</v>
+      </c>
       <c r="G9">
         <v>2</v>
       </c>
       <c r="H9">
-        <f t="shared" ref="H9:H21" ca="1" si="0">_xlfn.XLOOKUP(RAND(),$B$7:$B$21,$A$7:$A$21,$B$4,1,1)</f>
-        <v>15</v>
+        <f t="shared" ref="H9:H21" ca="1" si="2">_xlfn.XLOOKUP(RAND(),$B$7:$B$21,$A$7:$A$21,$B$4,1,1)</f>
+        <v>11</v>
       </c>
       <c r="I9">
         <f ca="1">I8+H9</f>
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J9">
-        <f t="shared" ref="J9:J21" ca="1" si="1">MAX(I9,L8+1)</f>
-        <v>31</v>
+        <f t="shared" ref="J9:J21" ca="1" si="3">MAX(I9,L8+1)</f>
+        <v>19</v>
       </c>
       <c r="K9">
-        <f t="shared" ref="K9:K21" ca="1" si="2">_xlfn.XLOOKUP(RAND(),$E$7:$E$21,$D$7:$D$21,$E$4,1,1)</f>
-        <v>15</v>
+        <f t="shared" ref="K9:K21" ca="1" si="4">_xlfn.XLOOKUP(RAND(),$E$7:$E$21,$D$7:$D$21,$E$4,1,1)</f>
+        <v>3</v>
       </c>
       <c r="L9">
-        <f t="shared" ref="L9:L21" ca="1" si="3">J9+K9</f>
-        <v>46</v>
+        <f t="shared" ref="L9:L21" ca="1" si="5">J9+K9</f>
+        <v>22</v>
       </c>
       <c r="M9">
         <f ca="1">J9-I9</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>4</v>
       </c>
-      <c r="B10" s="18"/>
+      <c r="B10" s="18">
+        <f t="shared" si="0"/>
+        <v>9.9632400487046024E-2</v>
+      </c>
       <c r="D10" s="8">
         <v>4</v>
       </c>
-      <c r="E10" s="18"/>
+      <c r="E10" s="18">
+        <f t="shared" si="1"/>
+        <v>0.63212055882855767</v>
+      </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>9</v>
       </c>
       <c r="I10">
-        <f t="shared" ref="I10:I14" ca="1" si="4">I9+H10</f>
-        <v>45</v>
+        <f t="shared" ref="I10:I14" ca="1" si="6">I9+H10</f>
+        <v>28</v>
       </c>
       <c r="J10">
-        <f t="shared" ca="1" si="1"/>
-        <v>47</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>28</v>
       </c>
       <c r="K10">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="L10">
-        <f t="shared" ca="1" si="3"/>
-        <v>62</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>29</v>
       </c>
       <c r="M10">
-        <f t="shared" ref="M10:M14" ca="1" si="5">J10-I10</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ref="M10:M14" ca="1" si="7">J10-I10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>5</v>
       </c>
-      <c r="B11" s="18"/>
+      <c r="B11" s="18">
+        <f t="shared" si="0"/>
+        <v>0.19123606207962526</v>
+      </c>
       <c r="D11" s="8">
         <v>5</v>
       </c>
-      <c r="E11" s="18"/>
+      <c r="E11" s="18">
+        <f t="shared" si="1"/>
+        <v>0.71349520313980985</v>
+      </c>
       <c r="G11">
         <v>4</v>
       </c>
       <c r="H11">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
       </c>
       <c r="I11">
+        <f t="shared" ca="1" si="6"/>
+        <v>41</v>
+      </c>
+      <c r="J11">
+        <f t="shared" ca="1" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="K11">
         <f t="shared" ca="1" si="4"/>
-        <v>60</v>
-      </c>
-      <c r="J11">
-        <f t="shared" ca="1" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="K11">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <f t="shared" ca="1" si="3"/>
-        <v>78</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>45</v>
       </c>
       <c r="M11">
-        <f t="shared" ca="1" si="5"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>6</v>
       </c>
-      <c r="B12" s="18"/>
+      <c r="B12" s="18">
+        <f t="shared" si="0"/>
+        <v>0.31337427753639757</v>
+      </c>
       <c r="D12" s="8">
         <v>6</v>
       </c>
-      <c r="E12" s="18"/>
+      <c r="E12" s="18">
+        <f t="shared" si="1"/>
+        <v>0.77686983985157021</v>
+      </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>10</v>
       </c>
       <c r="I12">
+        <f t="shared" ca="1" si="6"/>
+        <v>51</v>
+      </c>
+      <c r="J12">
+        <f t="shared" ca="1" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="K12">
         <f t="shared" ca="1" si="4"/>
-        <v>75</v>
-      </c>
-      <c r="J12">
-        <f t="shared" ca="1" si="1"/>
-        <v>79</v>
-      </c>
-      <c r="K12">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L12">
-        <f t="shared" ca="1" si="3"/>
-        <v>94</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>62</v>
       </c>
       <c r="M12">
-        <f t="shared" ca="1" si="5"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>7</v>
       </c>
-      <c r="B13" s="18"/>
+      <c r="B13" s="18">
+        <f t="shared" si="0"/>
+        <v>0.45296080948699424</v>
+      </c>
       <c r="D13" s="8">
         <v>7</v>
       </c>
-      <c r="E13" s="18"/>
+      <c r="E13" s="18">
+        <f t="shared" si="1"/>
+        <v>0.82622605654955483</v>
+      </c>
       <c r="G13">
         <v>6</v>
       </c>
       <c r="H13">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
       </c>
       <c r="I13">
+        <f t="shared" ca="1" si="6"/>
+        <v>58</v>
+      </c>
+      <c r="J13">
+        <f t="shared" ca="1" si="3"/>
+        <v>63</v>
+      </c>
+      <c r="K13">
         <f t="shared" ca="1" si="4"/>
-        <v>90</v>
-      </c>
-      <c r="J13">
-        <f t="shared" ca="1" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="K13">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <f t="shared" ca="1" si="3"/>
-        <v>110</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>65</v>
       </c>
       <c r="M13">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="7"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>8</v>
       </c>
-      <c r="B14" s="18"/>
+      <c r="B14" s="18">
+        <f t="shared" si="0"/>
+        <v>0.59254734143759147</v>
+      </c>
       <c r="D14" s="8">
         <v>8</v>
       </c>
-      <c r="E14" s="18"/>
+      <c r="E14" s="18">
+        <f t="shared" si="1"/>
+        <v>0.8646647167633873</v>
+      </c>
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
       </c>
       <c r="I14">
+        <f t="shared" ca="1" si="6"/>
+        <v>65</v>
+      </c>
+      <c r="J14">
+        <f t="shared" ca="1" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="K14">
         <f t="shared" ca="1" si="4"/>
-        <v>105</v>
-      </c>
-      <c r="J14">
-        <f t="shared" ca="1" si="1"/>
-        <v>111</v>
-      </c>
-      <c r="K14">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <f t="shared" ca="1" si="3"/>
-        <v>126</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>67</v>
       </c>
       <c r="M14">
-        <f t="shared" ca="1" si="5"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>9</v>
       </c>
-      <c r="B15" s="18"/>
+      <c r="B15" s="18">
+        <f t="shared" si="0"/>
+        <v>0.71662425872701097</v>
+      </c>
       <c r="D15" s="8">
         <v>9</v>
       </c>
-      <c r="E15" s="18"/>
+      <c r="E15" s="18">
+        <f t="shared" si="1"/>
+        <v>0.89460077543813565</v>
+      </c>
       <c r="G15">
         <v>8</v>
       </c>
       <c r="H15">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
       </c>
       <c r="I15">
-        <f t="shared" ref="I15:I21" ca="1" si="6">I14+H15</f>
-        <v>120</v>
+        <f t="shared" ref="I15:I21" ca="1" si="8">I14+H15</f>
+        <v>71</v>
       </c>
       <c r="J15">
-        <f t="shared" ca="1" si="1"/>
-        <v>127</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>71</v>
       </c>
       <c r="K15">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>10</v>
       </c>
       <c r="L15">
-        <f t="shared" ca="1" si="3"/>
-        <v>142</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>81</v>
       </c>
       <c r="M15">
-        <f t="shared" ref="M15:M21" ca="1" si="7">J15-I15</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ref="M15:M21" ca="1" si="9">J15-I15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>10</v>
       </c>
-      <c r="B16" s="18"/>
+      <c r="B16" s="18">
+        <f t="shared" si="0"/>
+        <v>0.81588579255854654</v>
+      </c>
       <c r="D16" s="8">
         <v>10</v>
       </c>
-      <c r="E16" s="18"/>
+      <c r="E16" s="18">
+        <f t="shared" si="1"/>
+        <v>0.91791500137610116</v>
+      </c>
       <c r="G16">
         <v>9</v>
       </c>
       <c r="H16">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>8</v>
       </c>
       <c r="I16">
-        <f t="shared" ca="1" si="6"/>
-        <v>135</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>79</v>
       </c>
       <c r="J16">
-        <f t="shared" ca="1" si="1"/>
-        <v>143</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>82</v>
       </c>
       <c r="K16">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
       </c>
       <c r="L16">
-        <f t="shared" ca="1" si="3"/>
-        <v>158</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>86</v>
       </c>
       <c r="M16">
-        <f t="shared" ca="1" si="7"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="9"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>11</v>
       </c>
-      <c r="B17" s="18"/>
+      <c r="B17" s="18">
+        <f t="shared" si="0"/>
+        <v>0.88807599898148137</v>
+      </c>
       <c r="D17" s="8">
         <v>11</v>
       </c>
-      <c r="E17" s="18"/>
+      <c r="E17" s="18">
+        <f t="shared" si="1"/>
+        <v>0.93607213879329243</v>
+      </c>
       <c r="G17">
         <v>10</v>
       </c>
       <c r="H17">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
       </c>
       <c r="I17">
-        <f t="shared" ca="1" si="6"/>
-        <v>150</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>85</v>
       </c>
       <c r="J17">
-        <f t="shared" ca="1" si="1"/>
-        <v>159</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>87</v>
       </c>
       <c r="K17">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
       </c>
       <c r="L17">
-        <f t="shared" ca="1" si="3"/>
-        <v>174</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>92</v>
       </c>
       <c r="M17">
-        <f t="shared" ca="1" si="7"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="9"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>12</v>
       </c>
-      <c r="B18" s="18"/>
+      <c r="B18" s="18">
+        <f t="shared" si="0"/>
+        <v>0.93620280326343808</v>
+      </c>
       <c r="D18" s="8">
         <v>12</v>
       </c>
-      <c r="E18" s="18"/>
+      <c r="E18" s="18">
+        <f t="shared" si="1"/>
+        <v>0.95021293163213605</v>
+      </c>
       <c r="G18">
         <v>11</v>
       </c>
       <c r="H18">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>12</v>
       </c>
       <c r="I18">
-        <f t="shared" ca="1" si="6"/>
-        <v>165</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>97</v>
       </c>
       <c r="J18">
-        <f t="shared" ca="1" si="1"/>
-        <v>175</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>97</v>
       </c>
       <c r="K18">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>8</v>
       </c>
       <c r="L18">
-        <f t="shared" ca="1" si="3"/>
-        <v>190</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>105</v>
       </c>
       <c r="M18">
-        <f t="shared" ca="1" si="7"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>13</v>
       </c>
-      <c r="B19" s="18"/>
+      <c r="B19" s="18">
+        <f t="shared" si="0"/>
+        <v>0.96581929820618062</v>
+      </c>
       <c r="D19" s="8">
         <v>13</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="18">
+        <f t="shared" si="1"/>
+        <v>0.96122579216827797</v>
+      </c>
       <c r="G19">
         <v>12</v>
       </c>
       <c r="H19">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>9</v>
       </c>
       <c r="I19">
-        <f t="shared" ca="1" si="6"/>
-        <v>180</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>106</v>
       </c>
       <c r="J19">
-        <f t="shared" ca="1" si="1"/>
-        <v>191</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>106</v>
       </c>
       <c r="K19">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5</v>
       </c>
       <c r="L19">
-        <f t="shared" ca="1" si="3"/>
-        <v>206</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>111</v>
       </c>
       <c r="M19">
-        <f t="shared" ca="1" si="7"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>14</v>
       </c>
-      <c r="B20" s="18"/>
+      <c r="B20" s="18">
+        <f t="shared" si="0"/>
+        <v>0.98274300960203353</v>
+      </c>
       <c r="D20" s="8">
         <v>14</v>
       </c>
-      <c r="E20" s="18"/>
+      <c r="E20" s="18">
+        <f t="shared" si="1"/>
+        <v>0.96980261657768152</v>
+      </c>
       <c r="G20">
         <v>13</v>
       </c>
       <c r="H20">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>10</v>
       </c>
       <c r="I20">
-        <f t="shared" ca="1" si="6"/>
-        <v>195</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>116</v>
       </c>
       <c r="J20">
-        <f t="shared" ca="1" si="1"/>
-        <v>207</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>116</v>
       </c>
       <c r="K20">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4</v>
       </c>
       <c r="L20">
-        <f t="shared" ca="1" si="3"/>
-        <v>222</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>120</v>
       </c>
       <c r="M20">
-        <f t="shared" ca="1" si="7"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="12">
         <v>15</v>
       </c>
@@ -1269,37 +1370,37 @@
         <v>14</v>
       </c>
       <c r="H21">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
       </c>
       <c r="I21">
-        <f t="shared" ca="1" si="6"/>
-        <v>210</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>120</v>
       </c>
       <c r="J21">
-        <f t="shared" ca="1" si="1"/>
-        <v>223</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>121</v>
       </c>
       <c r="K21">
-        <f t="shared" ca="1" si="2"/>
-        <v>15</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1</v>
       </c>
       <c r="L21">
-        <f t="shared" ca="1" si="3"/>
-        <v>238</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>122</v>
       </c>
       <c r="M21">
-        <f t="shared" ca="1" si="7"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <f t="shared" ca="1" si="9"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L22" s="5" t="s">
         <v>13</v>
       </c>
       <c r="M22" s="2">
         <f ca="1">SUM(M7:M21)</f>
-        <v>91</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
